--- a/data/trans_bre/IP19C03-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP19C03-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,49 +660,49 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-23,1; 11,28</t>
+          <t>-25,37; 12,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,52; 12,19</t>
+          <t>-25,08; 13,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 31,37</t>
+          <t>-3,97; 30,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,59; 24,07</t>
+          <t>-16,44; 23,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-79,62; 102,51</t>
+          <t>-82,4; 123,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-75,83; 90,89</t>
+          <t>-72,62; 94,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-20,78; 483,16</t>
+          <t>-24,27; 474,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-41,62; 109,87</t>
+          <t>-40,0; 102,57</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 12,34</t>
+          <t>-11,64; 12,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-21,92; -1,75</t>
+          <t>-21,83; -1,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-21,28; 6,7</t>
+          <t>-20,61; 6,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 16,77</t>
+          <t>-11,61; 19,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-42,09; 73,1</t>
+          <t>-43,69; 75,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-85,8; -3,83</t>
+          <t>-86,46; 6,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-60,77; 34,24</t>
+          <t>-59,43; 31,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-39,87; 93,3</t>
+          <t>-39,27; 118,36</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 26,17</t>
+          <t>-5,64; 25,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 9,84</t>
+          <t>-12,04; 11,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 9,85</t>
+          <t>-13,58; 10,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,48; 5,29</t>
+          <t>-19,85; 5,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-29,72; 277,91</t>
+          <t>-30,59; 262,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-74,09; 199,5</t>
+          <t>-73,75; 212,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-100,0; 384,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-84,06; 101,68</t>
+          <t>-87,55; 89,49</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 19,2</t>
+          <t>-4,45; 21,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 26,33</t>
+          <t>-5,18; 24,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 20,6</t>
+          <t>-4,27; 19,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 22,47</t>
+          <t>-9,35; 21,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,31; 271,57</t>
+          <t>-26,98; 288,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,43; 257,86</t>
+          <t>-23,52; 197,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,67; 272,91</t>
+          <t>-25,28; 271,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-51,68; 409,53</t>
+          <t>-50,97; 395,13</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-23,19; 14,91</t>
+          <t>-22,28; 16,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 19,79</t>
+          <t>-7,56; 20,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 31,26</t>
+          <t>-18,11; 32,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 18,79</t>
+          <t>-8,58; 16,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-70,41; 155,2</t>
+          <t>-70,32; 156,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-73,04; 795,74</t>
+          <t>-74,84; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-61,68; 283,44</t>
+          <t>-61,4; 307,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-51,55; 304,18</t>
+          <t>-47,13; 247,85</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,49 +1160,49 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 27,32</t>
+          <t>-3,33; 27,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 19,5</t>
+          <t>-10,01; 19,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 4,39</t>
+          <t>-15,03; 4,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,99; 10,83</t>
+          <t>-17,2; 10,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,37; 679,48</t>
+          <t>-30,57; 601,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-56,01; 302,82</t>
+          <t>-55,11; 370,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 190,56</t>
+          <t>-100,0; 279,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-82,04; 234,0</t>
+          <t>-80,98; 226,31</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 8,43</t>
+          <t>-10,38; 10,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 13,66</t>
+          <t>-10,19; 12,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,04; 0,36</t>
+          <t>-16,94; 0,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 9,25</t>
+          <t>-10,95; 9,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-54,01; 83,02</t>
+          <t>-57,4; 118,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-48,13; 145,05</t>
+          <t>-48,26; 117,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-89,35; 26,87</t>
+          <t>-90,1; 23,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-46,96; 64,48</t>
+          <t>-46,66; 69,51</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 16,54</t>
+          <t>-5,88; 16,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 16,5</t>
+          <t>-8,55; 15,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 11,23</t>
+          <t>-12,96; 10,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 6,47</t>
+          <t>-5,78; 6,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,18; 116,62</t>
+          <t>-24,58; 113,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-23,93; 63,7</t>
+          <t>-23,11; 60,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-40,22; 54,2</t>
+          <t>-37,95; 50,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-68,32; 205,54</t>
+          <t>-68,39; 189,14</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 7,87</t>
+          <t>-1,19; 8,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 6,02</t>
+          <t>-3,85; 6,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 3,43</t>
+          <t>-6,27; 3,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 6,07</t>
+          <t>-3,22; 6,53</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 51,36</t>
+          <t>-5,77; 55,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-16,24; 36,2</t>
+          <t>-17,58; 36,25</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-26,95; 22,16</t>
+          <t>-29,57; 19,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 43,57</t>
+          <t>-17,46; 46,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C03-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP19C03-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-25,37; 12,65</t>
+          <t>-25,97; 10,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 13,51</t>
+          <t>-24,35; 14,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 30,18</t>
+          <t>-3,39; 30,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,44; 23,13</t>
+          <t>-16,69; 23,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-82,4; 123,0</t>
+          <t>-80,49; 111,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-72,62; 94,63</t>
+          <t>-73,46; 92,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-24,27; 474,23</t>
+          <t>-20,85; 465,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-40,0; 102,57</t>
+          <t>-40,47; 107,61</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 12,08</t>
+          <t>-12,8; 11,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-21,83; -1,35</t>
+          <t>-20,34; -0,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-20,61; 6,44</t>
+          <t>-20,02; 5,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 19,85</t>
+          <t>-10,76; 19,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,69; 75,76</t>
+          <t>-48,37; 73,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-86,46; 6,06</t>
+          <t>-84,15; 7,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-59,43; 31,98</t>
+          <t>-58,12; 34,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-39,27; 118,36</t>
+          <t>-36,46; 105,06</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 25,95</t>
+          <t>-5,56; 25,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 11,55</t>
+          <t>-14,18; 10,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 10,41</t>
+          <t>-14,31; 9,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,85; 5,34</t>
+          <t>-18,68; 5,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-30,59; 262,19</t>
+          <t>-30,76; 262,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-73,75; 212,16</t>
+          <t>-79,41; 207,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 384,23</t>
+          <t>-100,0; 282,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-87,55; 89,49</t>
+          <t>-85,08; 104,07</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 21,07</t>
+          <t>-4,15; 20,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 24,87</t>
+          <t>-6,09; 24,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 19,88</t>
+          <t>-5,07; 19,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 21,56</t>
+          <t>-9,78; 23,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,98; 288,46</t>
+          <t>-26,42; 309,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,52; 197,72</t>
+          <t>-24,4; 195,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-25,28; 271,68</t>
+          <t>-31,1; 275,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,97; 395,13</t>
+          <t>-48,26; 416,11</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-22,28; 16,25</t>
+          <t>-24,13; 13,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 20,28</t>
+          <t>-7,2; 19,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,11; 32,68</t>
+          <t>-18,17; 30,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 16,66</t>
+          <t>-7,52; 18,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-70,32; 156,84</t>
+          <t>-77,26; 126,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-74,84; —</t>
+          <t>-74,54; 850,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-61,4; 307,71</t>
+          <t>-61,92; 272,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-47,13; 247,85</t>
+          <t>-51,81; 289,65</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 27,05</t>
+          <t>-3,55; 28,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 19,51</t>
+          <t>-9,1; 18,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,03; 4,59</t>
+          <t>-14,84; 5,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,2; 10,41</t>
+          <t>-17,1; 10,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,57; 601,45</t>
+          <t>-38,88; 671,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-55,11; 370,75</t>
+          <t>-51,89; 262,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 279,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-80,98; 226,31</t>
+          <t>-80,81; 333,19</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 10,0</t>
+          <t>-10,05; 9,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 12,4</t>
+          <t>-9,22; 10,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,94; 0,66</t>
+          <t>-18,1; 0,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 9,96</t>
+          <t>-11,68; 10,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-57,4; 118,39</t>
+          <t>-53,42; 104,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-48,26; 117,86</t>
+          <t>-44,97; 101,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-90,1; 23,46</t>
+          <t>-91,13; 15,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-46,66; 69,51</t>
+          <t>-48,3; 72,91</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 16,14</t>
+          <t>-5,95; 16,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 15,8</t>
+          <t>-8,82; 15,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 10,45</t>
+          <t>-13,03; 9,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 6,57</t>
+          <t>-5,05; 6,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,58; 113,36</t>
+          <t>-24,58; 113,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-23,11; 60,8</t>
+          <t>-23,29; 61,32</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-37,95; 50,27</t>
+          <t>-39,67; 44,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-68,39; 189,14</t>
+          <t>-65,14; 235,33</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 8,08</t>
+          <t>-1,11; 8,28</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 6,07</t>
+          <t>-3,58; 5,76</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 3,18</t>
+          <t>-5,9; 3,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 6,53</t>
+          <t>-3,75; 6,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 55,01</t>
+          <t>-5,84; 53,74</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 36,25</t>
+          <t>-15,87; 33,59</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-29,57; 19,71</t>
+          <t>-28,37; 19,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-17,46; 46,99</t>
+          <t>-19,62; 43,85</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C03-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP19C03-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,71</t>
+          <t>10,55</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>36,17%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-25,97; 10,48</t>
+          <t>-23,1; 11,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,35; 14,31</t>
+          <t>-25,52; 12,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 30,96</t>
+          <t>-2,81; 31,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,69; 23,28</t>
+          <t>-9,07; 29,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-80,49; 111,12</t>
+          <t>-79,62; 102,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-73,46; 92,78</t>
+          <t>-75,83; 90,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 465,82</t>
+          <t>-20,78; 483,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-40,47; 107,61</t>
+          <t>-23,26; 144,48</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,01</t>
+          <t>-0,48</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>-1,94%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,8; 11,82</t>
+          <t>-11,05; 12,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-20,34; -0,43</t>
+          <t>-21,92; -1,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-20,02; 5,81</t>
+          <t>-21,28; 6,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 19,2</t>
+          <t>-14,92; 11,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-48,37; 73,9</t>
+          <t>-42,09; 73,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-84,15; 7,23</t>
+          <t>-85,8; -3,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-58,12; 34,31</t>
+          <t>-60,77; 34,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,46; 105,06</t>
+          <t>-47,14; 63,38</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-5,93</t>
+          <t>-4,98</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-40,68%</t>
+          <t>-34,9%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 25,85</t>
+          <t>-4,7; 26,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 10,56</t>
+          <t>-12,19; 9,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,31; 9,63</t>
+          <t>-13,62; 9,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,68; 5,83</t>
+          <t>-17,48; 6,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-30,76; 262,91</t>
+          <t>-29,72; 277,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-79,41; 207,95</t>
+          <t>-74,09; 199,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 282,92</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-85,08; 104,07</t>
+          <t>-82,12; 125,49</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,94</t>
+          <t>4,94</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>35,07%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 20,0</t>
+          <t>-5,21; 19,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 24,09</t>
+          <t>-6,64; 26,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 19,25</t>
+          <t>-3,79; 20,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 23,11</t>
+          <t>-11,39; 21,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,42; 309,95</t>
+          <t>-27,31; 271,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,4; 195,01</t>
+          <t>-23,43; 257,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,1; 275,9</t>
+          <t>-24,67; 272,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,26; 416,11</t>
+          <t>-55,39; 369,94</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,04</t>
+          <t>4,97</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>42,21%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-24,13; 13,62</t>
+          <t>-23,19; 14,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 19,08</t>
+          <t>-7,42; 19,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,17; 30,39</t>
+          <t>-18,57; 31,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 18,18</t>
+          <t>-8,24; 18,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-77,26; 126,07</t>
+          <t>-70,41; 155,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-74,54; 850,84</t>
+          <t>-73,04; 795,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-61,92; 272,66</t>
+          <t>-61,68; 283,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-51,81; 289,65</t>
+          <t>-52,83; 293,63</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-2,38</t>
+          <t>-1,62</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-18,46%</t>
+          <t>-12,98%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 28,96</t>
+          <t>-3,9; 27,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 18,12</t>
+          <t>-10,05; 19,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 5,11</t>
+          <t>-13,79; 4,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 10,81</t>
+          <t>-16,13; 11,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-38,88; 671,23</t>
+          <t>-32,37; 679,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-51,89; 262,91</t>
+          <t>-56,01; 302,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 190,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-80,81; 333,19</t>
+          <t>-80,97; 260,63</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,99</t>
+          <t>-0,43</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-5,05%</t>
+          <t>-2,14%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 9,36</t>
+          <t>-10,38; 8,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 10,66</t>
+          <t>-9,38; 13,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,1; 0,11</t>
+          <t>-17,04; 0,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 10,1</t>
+          <t>-11,17; 10,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-53,42; 104,67</t>
+          <t>-54,01; 83,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-44,97; 101,75</t>
+          <t>-48,13; 145,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-91,13; 15,47</t>
+          <t>-89,35; 26,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-48,3; 72,91</t>
+          <t>-45,41; 67,09</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 16,06</t>
+          <t>-4,68; 16,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 15,49</t>
+          <t>-9,82; 16,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 9,58</t>
+          <t>-13,05; 11,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 6,57</t>
+          <t>-5,32; 6,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,58; 113,13</t>
+          <t>-22,18; 116,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-23,29; 61,32</t>
+          <t>-23,93; 63,7</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-39,67; 44,76</t>
+          <t>-40,22; 54,2</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-65,14; 235,33</t>
+          <t>-69,81; 219,47</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1,33</t>
+          <t>1,18</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 8,28</t>
+          <t>-1,56; 7,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 5,76</t>
+          <t>-3,68; 6,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 3,11</t>
+          <t>-5,63; 3,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 6,28</t>
+          <t>-3,43; 5,54</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 53,74</t>
+          <t>-8,24; 51,36</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 33,59</t>
+          <t>-16,24; 36,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-28,37; 19,42</t>
+          <t>-26,95; 22,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 43,85</t>
+          <t>-19,66; 40,05</t>
         </is>
       </c>
     </row>
